--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487527_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487527_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.749</v>
+        <v>7.7517</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2493</v>
+        <v>6.5727</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4997</v>
+        <v>1.179</v>
       </c>
       <c r="G2" t="n">
         <v>3.4193</v>
@@ -610,13 +610,13 @@
         <v>0.9792</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8377</v>
+        <v>0.8404</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0047</v>
+        <v>0.3282</v>
       </c>
       <c r="U2" t="n">
-        <v>0.833</v>
+        <v>0.5123</v>
       </c>
       <c r="V2" t="n">
         <v>2.7086</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. GUERRA TRUJILLO</t>
+          <t>M. ALVAREZ HERNAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7835</v>
+        <v>3.9349</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1174</v>
+        <v>1.4554</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6661</v>
+        <v>2.4795</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8784</v>
+        <v>2.1182</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8918</v>
+        <v>-0.0902</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9866</v>
+        <v>2.2084</v>
       </c>
       <c r="J3" t="n">
-        <v>3.839</v>
+        <v>1.2611</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2928</v>
+        <v>0.039</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5462</v>
+        <v>1.2221</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0395</v>
+        <v>0.8571</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.401</v>
+        <v>-0.1292</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4405</v>
+        <v>0.9863</v>
       </c>
       <c r="P3" t="n">
-        <v>-6.8547</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q3" t="n">
-        <v>-8.0298</v>
+        <v>-3.1336</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1751</v>
+        <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3841</v>
+        <v>0.1462</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9326</v>
+        <v>0.2864</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4515</v>
+        <v>-0.1403</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3756</v>
+        <v>3.0415</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3756</v>
+        <v>3.0415</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6437</v>
+        <v>2.887</v>
       </c>
       <c r="E4" t="n">
-        <v>0.638</v>
+        <v>0.9615</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0057</v>
+        <v>1.9255</v>
       </c>
       <c r="G4" t="n">
         <v>2.1954</v>
@@ -766,13 +766,13 @@
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0229</v>
+        <v>0.2204</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0129</v>
+        <v>0.3105</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0901</v>
       </c>
       <c r="V4" t="n">
         <v>0.2754</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ALVAREZ HERNAN</t>
+          <t>D. GUERRA TRUJILLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2047</v>
+        <v>0.8129</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3132</v>
+        <v>-1.0512</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8914</v>
+        <v>1.8642</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1182</v>
+        <v>3.8784</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0902</v>
+        <v>0.8918</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2084</v>
+        <v>2.9866</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2611</v>
+        <v>3.839</v>
       </c>
       <c r="K5" t="n">
-        <v>0.039</v>
+        <v>1.2928</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2221</v>
+        <v>2.5462</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8571</v>
+        <v>0.0395</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1292</v>
+        <v>-0.401</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9863</v>
+        <v>0.4405</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3709</v>
+        <v>-6.8547</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1336</v>
+        <v>-8.0298</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7626</v>
+        <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5841</v>
+        <v>1.4136</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8557</v>
+        <v>0.764</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7282999999999999</v>
+        <v>0.6496</v>
       </c>
       <c r="V5" t="n">
-        <v>3.0415</v>
+        <v>2.3756</v>
       </c>
       <c r="W5" t="n">
-        <v>3.0415</v>
+        <v>2.3756</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.212</v>
+        <v>-1.3457</v>
       </c>
       <c r="E6" t="n">
         <v>-1.7784</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5664</v>
+        <v>0.4327</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4825</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2497</v>
+        <v>0.116</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4279</v>
+        <v>0.2942</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4117</v>
+        <v>-1.4676</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8022</v>
+        <v>1.4522</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.2138</v>
+        <v>-2.9198</v>
       </c>
       <c r="G7" t="n">
         <v>0.8141</v>
@@ -1000,13 +1000,13 @@
         <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.249</v>
+        <v>0.1931</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6693</v>
+        <v>0.3194</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4203</v>
+        <v>-0.1263</v>
       </c>
       <c r="V7" t="n">
         <v>-3.6498</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6489</v>
+        <v>-1.9943</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4281</v>
+        <v>-1.8804</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2208</v>
+        <v>-0.1139</v>
       </c>
       <c r="G8" t="n">
         <v>0.8345</v>
@@ -1078,13 +1078,13 @@
         <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>0.967</v>
+        <v>0.6217</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0851</v>
+        <v>0.6328</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1181</v>
+        <v>-0.0112</v>
       </c>
       <c r="V8" t="n">
         <v>-1.492</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8599</v>
+        <v>-2.7366</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.938</v>
+        <v>-3.1622</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0781</v>
+        <v>0.4256</v>
       </c>
       <c r="G9" t="n">
         <v>1.5963</v>
@@ -1156,13 +1156,13 @@
         <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2869</v>
+        <v>-0.1636</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6952</v>
+        <v>0.0806</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5917</v>
+        <v>-0.2442</v>
       </c>
       <c r="V9" t="n">
         <v>-0.4481</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>7.248399999999998</v>
+        <v>7.842299999999998</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9756</v>
+        <v>2.5696</v>
       </c>
       <c r="F10" t="n">
-        <v>5.272799999999998</v>
+        <v>5.2728</v>
       </c>
       <c r="G10" t="n">
         <v>14.3737</v>
@@ -1231,16 +1231,16 @@
         <v>-21.5433</v>
       </c>
       <c r="R10" t="n">
-        <v>8.812999999999999</v>
+        <v>8.813000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7936</v>
+        <v>3.3878</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9497</v>
+        <v>2.5437</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8441000000000001</v>
+        <v>0.844</v>
       </c>
       <c r="V10" t="n">
         <v>2.811199999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8447</v>
+        <v>2.2734</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0465</v>
+        <v>3.1488</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2017</v>
+        <v>-0.8754</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7124</v>
@@ -1312,13 +1312,13 @@
         <v>4.1128</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8554</v>
+        <v>-0.4267</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3999</v>
+        <v>-0.2976</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4554</v>
+        <v>-0.1291</v>
       </c>
       <c r="V11" t="n">
         <v>2.4332</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.7432</v>
+        <v>1.6187</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3063</v>
+        <v>1.1016</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4369</v>
+        <v>0.5171</v>
       </c>
       <c r="G12" t="n">
         <v>0.794</v>
@@ -1390,13 +1390,13 @@
         <v>0.5875</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3616</v>
+        <v>0.2372</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4446</v>
+        <v>0.24</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.083</v>
+        <v>-0.0028</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. MUJICA LANDAETA</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2153</v>
+        <v>0.7271</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2018</v>
+        <v>0.4725</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9865</v>
+        <v>0.2546</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2932</v>
+        <v>-0.725</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7927999999999999</v>
+        <v>-1.9167</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.086</v>
+        <v>1.1917</v>
       </c>
       <c r="J13" t="n">
-        <v>2.2036</v>
+        <v>1.6332</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0823</v>
+        <v>-0.7658</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1212</v>
+        <v>2.399</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.4968</v>
+        <v>-2.3582</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2895</v>
+        <v>-1.151</v>
       </c>
       <c r="O13" t="n">
         <v>-1.2073</v>
       </c>
       <c r="P13" t="n">
-        <v>2.546</v>
+        <v>0.7834</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1958</v>
+        <v>-1.9585</v>
       </c>
       <c r="R13" t="n">
         <v>2.7419</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3381</v>
+        <v>-0.5478</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1941</v>
+        <v>-0.4188</v>
       </c>
       <c r="U13" t="n">
-        <v>0.144</v>
+        <v>-0.1291</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.3756</v>
+        <v>1.2166</v>
       </c>
       <c r="W13" t="n">
+        <v>1.2166</v>
+      </c>
+      <c r="X13" t="n">
         <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-2.3756</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>S. MUJICA LANDAETA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2677</v>
+        <v>-0.0225</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6531</v>
+        <v>2.2018</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3854</v>
+        <v>-2.2243</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.725</v>
+        <v>-0.2932</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.9167</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1917</v>
+        <v>-1.086</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6332</v>
+        <v>2.2036</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7658</v>
+        <v>2.0823</v>
       </c>
       <c r="L14" t="n">
-        <v>2.399</v>
+        <v>0.1212</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3582</v>
+        <v>-2.4968</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.151</v>
+        <v>-1.2895</v>
       </c>
       <c r="O14" t="n">
         <v>-1.2073</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7834</v>
+        <v>2.546</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9585</v>
+        <v>-0.1958</v>
       </c>
       <c r="R14" t="n">
         <v>2.7419</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5427</v>
+        <v>0.1003</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5445</v>
+        <v>0.1941</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0018</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2166</v>
+        <v>-2.3756</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.3756</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. GARCÍA SINDIN</t>
+          <t>N. BARREIRO BUCETA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.2996</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.0932</v>
+        <v>-2.0531</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7936</v>
+        <v>1.3167</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8878</v>
+        <v>-2.6195</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2504</v>
+        <v>0.3523</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.6374</v>
+        <v>-2.9718</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.618</v>
+        <v>-0.8686</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4287</v>
+        <v>1.1637</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.0467</v>
+        <v>-2.0322</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2698</v>
+        <v>-1.751</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6791</v>
+        <v>-0.8114</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4093</v>
+        <v>-0.9396</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9792</v>
+        <v>1.7626</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9792</v>
+        <v>2.9377</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.724</v>
+        <v>0.0629</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4752</v>
+        <v>-0.0094</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2488</v>
+        <v>0.0723</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3329</v>
+        <v>0.0576</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3329</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ PILLADO</t>
+          <t>L. GARCÍA SINDIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.4227</v>
+        <v>-1.0608</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.9529</v>
+        <v>-1.9909</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5302</v>
+        <v>0.9301</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.3448</v>
+        <v>-1.8878</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4298</v>
+        <v>-0.2504</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.9151</v>
+        <v>-1.6374</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.2688</v>
+        <v>-1.618</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0256</v>
+        <v>0.4287</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2432</v>
+        <v>-2.0467</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.076</v>
+        <v>-0.2698</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4041</v>
+        <v>-0.6791</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6719000000000001</v>
+        <v>0.4093</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.546</v>
+        <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1595</v>
+        <v>-0.4852</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4911</v>
+        <v>-0.3729</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3316</v>
+        <v>-0.1123</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6083</v>
+        <v>0.3329</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6083</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. BARREIRO BUCETA</t>
+          <t>J. FERNANDEZ PILLADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6961</v>
+        <v>-1.7933</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.7694</v>
+        <v>-2.5669</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0733</v>
+        <v>0.7735</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.6195</v>
+        <v>-2.3448</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3523</v>
+        <v>-0.4298</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.9718</v>
+        <v>-1.9151</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8686</v>
+        <v>-1.2688</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1637</v>
+        <v>-0.0256</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.0322</v>
+        <v>-1.2432</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.751</v>
+        <v>-1.076</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8114</v>
+        <v>-0.4041</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9396</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7626</v>
+        <v>1.3709</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9377</v>
+        <v>2.546</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8968</v>
+        <v>-0.2111</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7258</v>
+        <v>-0.1229</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.171</v>
+        <v>-0.0882</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0576</v>
+        <v>-0.6083</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0576</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4092</v>
+        <v>-3.1283</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.14</v>
+        <v>-2.2657</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2692</v>
+        <v>-0.8626</v>
       </c>
       <c r="G18" t="n">
         <v>-2.8086</v>
@@ -1858,13 +1858,13 @@
         <v>2.7419</v>
       </c>
       <c r="S18" t="n">
-        <v>0.699</v>
+        <v>-0.0201</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1251</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4261</v>
+        <v>-0.0196</v>
       </c>
       <c r="V18" t="n">
         <v>-3.0415</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.9562</v>
+        <v>-3.7617</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2186</v>
+        <v>-3.321</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7376</v>
+        <v>-0.4407</v>
       </c>
       <c r="G19" t="n">
         <v>-3.7764</v>
@@ -1936,13 +1936,13 @@
         <v>2.1543</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.333</v>
+        <v>-0.1385</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0465</v>
+        <v>-0.0559</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3795</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8260999999999999</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-7.2483</v>
+        <v>-5.883799999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.272599999999999</v>
+        <v>-5.2729</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9756</v>
+        <v>-0.6110000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-14.3737</v>
@@ -2014,13 +2014,13 @@
         <v>21.5432</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.7937</v>
+        <v>-1.429</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8440000000000001</v>
+        <v>-0.844</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.9496</v>
+        <v>-0.5851999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-2.8112</v>
